--- a/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/04/2026 đến ngày 13/04/2026</t>
+          <t>Từ ngày 01/04/2026 đến ngày 18/04/2026</t>
         </is>
       </c>
     </row>

--- a/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/04/2026 đến ngày 18/04/2026</t>
+          <t>Từ ngày 01/04/2026 đến ngày 24/04/2026</t>
         </is>
       </c>
     </row>
@@ -771,6 +771,89 @@
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Số 245A Lê Lợi, Phường Vũng Tàu, thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>5364000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>5364000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuKhongMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/04/2026 đến ngày 24/04/2026</t>
+          <t>Từ ngày 01/04/2026 đến ngày 30/04/2026</t>
         </is>
       </c>
     </row>
@@ -325,12 +325,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K26THE</t>
+          <t>K26TBB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>387215</t>
+          <t>109490</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -340,12 +340,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0300954529</t>
+          <t>0100111948-043</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN CÔNG THƯƠNG VIỆT NAM - CHI NHÁNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -355,20 +355,20 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
         </is>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="13" t="n">
-        <v>163453.0</v>
+        <v>35000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>16345.0</v>
+        <v>3500.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>179798.0</v>
+        <v>38500.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -407,7 +407,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>387217</t>
+          <t>387215</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -437,15 +437,15 @@
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="13" t="n">
-        <v>191818.0</v>
+        <v>163453.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>19182.0</v>
+        <v>16345.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>211000.0</v>
+        <v>179798.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>387218</t>
+          <t>387217</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -514,15 +514,15 @@
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="13" t="n">
-        <v>163636.0</v>
+        <v>191818.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>16364.0</v>
+        <v>19182.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>180000.0</v>
+        <v>211000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K26TKE</t>
+          <t>K26THE</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>127239</t>
+          <t>387218</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -591,15 +591,15 @@
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="13" t="n">
-        <v>8000.0</v>
+        <v>163636.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>800.0</v>
+        <v>16364.0</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>8800.0</v>
+        <v>180000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>127244</t>
+          <t>127239</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>127254</t>
+          <t>127244</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>K26TAA</t>
+          <t>K26TKE</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>127254</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -817,43 +817,278 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Số 245A Lê Lợi, Phường Vũng Tàu, thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="13" t="n">
-        <v>5364000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>800.0</v>
+      </c>
+      <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
+        <v>8800.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>699510</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="13" t="n">
+        <v>139560.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>8135.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>147695.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>699514</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="13" t="n">
+        <v>1006760.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>58725.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1065485.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Số 245A Lê Lợi, Phường Vũng Tàu, thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
         <v>5364000.0</v>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="L16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>5364000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
